--- a/3학년 2학기/기인프/중간고사/신규 채점 (에러 관련 재채점)/1번 문제 과제평가 중간 시험 제출_기초인공지능프로그래밍_20261026_재채점.xlsx
+++ b/3학년 2학기/기인프/중간고사/신규 채점 (에러 관련 재채점)/1번 문제 과제평가 중간 시험 제출_기초인공지능프로그래밍_20261026_재채점.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\SOGANG\3학년 2학기\기인프\중간고사\신규 채점 (에러 관련 재채점)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DF14B-FB97-483A-8E45-3E305827FBA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9570"/>
   </bookViews>
   <sheets>
     <sheet name="과제평가" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">과제평가!$A$4:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">과제평가!$B$4:$M$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1610,7 +1609,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2076,26 +2075,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M63"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" style="6" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="6" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="29" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="16.8984375" style="6" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" style="6" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="26.69921875" style="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="16.19921875" style="6" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="31.69921875" style="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="12.59765625" style="6" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="59.3984375" style="6" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.59765625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="6" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="6" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="6" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.75" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="6" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="31.75" style="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="6" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="59.375" style="6" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.625" style="6" customWidth="1"/>
     <col min="12" max="12" width="145" style="6" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="145" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2111,7 +2110,7 @@
       <c r="K1" s="12"/>
       <c r="L1" s="13"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -2125,7 +2124,7 @@
       <c r="K2" s="15"/>
       <c r="L2" s="16"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2166,7 +2165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2205,7 +2204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="289.8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="299.25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2244,7 +2243,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="289.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="299.25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2318,7 +2317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -2509,7 +2508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -2589,7 +2588,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -2628,7 +2627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2864,7 +2863,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2903,7 +2902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2981,7 +2980,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -3098,7 +3097,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -3215,7 +3214,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -3295,7 +3294,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -3336,7 +3335,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -3416,7 +3415,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -3455,7 +3454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -3806,7 +3805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -3884,7 +3883,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -3923,7 +3922,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -3962,7 +3961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -4044,7 +4043,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -4083,7 +4082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -4122,7 +4121,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -4161,7 +4160,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -4200,7 +4199,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -4239,7 +4238,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -4278,7 +4277,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -4356,7 +4355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" ht="396" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="400.2" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" ht="379.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -4436,7 +4435,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="365.4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -4478,11 +4477,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState ref="A5:L63">
-      <sortCondition ref="B4"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="B4:M4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
